--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/15.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/15.xlsx
@@ -426,13 +426,13 @@
         <v>-18.56653690649618</v>
       </c>
       <c r="E2">
-        <v>-18.34671148459737</v>
+        <v>-18.53184908745296</v>
       </c>
       <c r="F2">
-        <v>-1.754338998816176</v>
+        <v>-1.336298418788989</v>
       </c>
       <c r="G2">
-        <v>-10.36214251524516</v>
+        <v>-7.09554536029089</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.38897980723966</v>
       </c>
       <c r="E3">
-        <v>-19.58551177718766</v>
+        <v>-18.22340113736851</v>
       </c>
       <c r="F3">
-        <v>-2.029423245937836</v>
+        <v>-1.70457317035819</v>
       </c>
       <c r="G3">
-        <v>-10.5743752069316</v>
+        <v>-6.781046836261233</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.16638308079125</v>
       </c>
       <c r="E4">
-        <v>-19.22488674958683</v>
+        <v>-17.74372252810603</v>
       </c>
       <c r="F4">
-        <v>-1.909278494570601</v>
+        <v>-1.133678923696827</v>
       </c>
       <c r="G4">
-        <v>-10.2446944707464</v>
+        <v>-6.029985064969016</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.91755894124225</v>
       </c>
       <c r="E5">
-        <v>-20.20465380046437</v>
+        <v>-18.06570608699941</v>
       </c>
       <c r="F5">
-        <v>-2.032247978781383</v>
+        <v>-1.208655285691613</v>
       </c>
       <c r="G5">
-        <v>-9.75593026969463</v>
+        <v>-7.472026159578458</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.64717610306728</v>
       </c>
       <c r="E6">
-        <v>-20.311294834871</v>
+        <v>-19.0799846382894</v>
       </c>
       <c r="F6">
-        <v>-1.935141781620808</v>
+        <v>-0.9660538095359303</v>
       </c>
       <c r="G6">
-        <v>-9.606037506416078</v>
+        <v>-6.811483447446642</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.36428826638341</v>
       </c>
       <c r="E7">
-        <v>-20.71897976435953</v>
+        <v>-19.38296672024659</v>
       </c>
       <c r="F7">
-        <v>-1.99158507971276</v>
+        <v>-1.58639744830741</v>
       </c>
       <c r="G7">
-        <v>-9.369927365441555</v>
+        <v>-6.271171255695999</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.08163733984945</v>
       </c>
       <c r="E8">
-        <v>-20.7829580451399</v>
+        <v>-20.63415238924786</v>
       </c>
       <c r="F8">
-        <v>-1.55925184851767</v>
+        <v>-0.6668731830342357</v>
       </c>
       <c r="G8">
-        <v>-9.168552235895312</v>
+        <v>-5.417331781497295</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.80099919726792</v>
       </c>
       <c r="E9">
-        <v>-22.01824424190024</v>
+        <v>-20.91915190092059</v>
       </c>
       <c r="F9">
-        <v>-1.779998507485294</v>
+        <v>-1.355446131304699</v>
       </c>
       <c r="G9">
-        <v>-9.25164917188825</v>
+        <v>-6.550390085518507</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.52099724699217</v>
       </c>
       <c r="E10">
-        <v>-23.23937442891259</v>
+        <v>-21.23309288997634</v>
       </c>
       <c r="F10">
-        <v>-1.367191552708994</v>
+        <v>-0.976082853681624</v>
       </c>
       <c r="G10">
-        <v>-9.000678378471003</v>
+        <v>-5.823783258508832</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.25136709647892</v>
       </c>
       <c r="E11">
-        <v>-23.30022806262767</v>
+        <v>-21.97128396644069</v>
       </c>
       <c r="F11">
-        <v>-1.264020049425121</v>
+        <v>-1.085781892099557</v>
       </c>
       <c r="G11">
-        <v>-8.751932253271058</v>
+        <v>-6.255969356211092</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.98742524936981</v>
       </c>
       <c r="E12">
-        <v>-23.85135240630917</v>
+        <v>-22.98390962471789</v>
       </c>
       <c r="F12">
-        <v>-1.219071177414414</v>
+        <v>-0.2144967741610089</v>
       </c>
       <c r="G12">
-        <v>-8.03348910550128</v>
+        <v>-5.756925088013586</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.7235907161664</v>
       </c>
       <c r="E13">
-        <v>-23.87513595179745</v>
+        <v>-23.31197492420357</v>
       </c>
       <c r="F13">
-        <v>-1.066477618144717</v>
+        <v>0.09265937369483934</v>
       </c>
       <c r="G13">
-        <v>-8.198045647928993</v>
+        <v>-6.944553387789923</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.47118834178499</v>
       </c>
       <c r="E14">
-        <v>-25.18181806976272</v>
+        <v>-22.38444382100451</v>
       </c>
       <c r="F14">
-        <v>-0.9082611009448173</v>
+        <v>0.3075875800251991</v>
       </c>
       <c r="G14">
-        <v>-7.611865259998873</v>
+        <v>-4.735536597324956</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.22639016412427</v>
       </c>
       <c r="E15">
-        <v>-25.70289145992932</v>
+        <v>-25.70476624816849</v>
       </c>
       <c r="F15">
-        <v>-0.8020395488838367</v>
+        <v>-0.3589615641070343</v>
       </c>
       <c r="G15">
-        <v>-7.203477862267264</v>
+        <v>-4.906078087877096</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-14.98639515846637</v>
       </c>
       <c r="E16">
-        <v>-26.23036811234276</v>
+        <v>-25.2064846676825</v>
       </c>
       <c r="F16">
-        <v>-0.6412260998761603</v>
+        <v>1.010390223540953</v>
       </c>
       <c r="G16">
-        <v>-6.885012341372239</v>
+        <v>-5.214781974632773</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-14.76297284636576</v>
       </c>
       <c r="E17">
-        <v>-27.18059139879425</v>
+        <v>-25.36386272487107</v>
       </c>
       <c r="F17">
-        <v>-0.332301387615335</v>
+        <v>0.9546195597800733</v>
       </c>
       <c r="G17">
-        <v>-6.492486368658986</v>
+        <v>-5.264210296204248</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-14.5501157001763</v>
       </c>
       <c r="E18">
-        <v>-27.80257277527377</v>
+        <v>-27.05889318831212</v>
       </c>
       <c r="F18">
-        <v>-0.09159521607725749</v>
+        <v>0.8795015469594085</v>
       </c>
       <c r="G18">
-        <v>-6.406938360161144</v>
+        <v>-4.42262946575163</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-14.34170100559937</v>
       </c>
       <c r="E19">
-        <v>-27.96476460033249</v>
+        <v>-27.68056662855911</v>
       </c>
       <c r="F19">
-        <v>0.0563917920654714</v>
+        <v>1.281095720571414</v>
       </c>
       <c r="G19">
-        <v>-5.653130206423671</v>
+        <v>-6.237450141729586</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-14.14367896357364</v>
       </c>
       <c r="E20">
-        <v>-29.38550539312895</v>
+        <v>-28.42195933614689</v>
       </c>
       <c r="F20">
-        <v>0.181032093327699</v>
+        <v>2.105554885964512</v>
       </c>
       <c r="G20">
-        <v>-5.67044849381442</v>
+        <v>-4.820451330061826</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-13.94615093825635</v>
       </c>
       <c r="E21">
-        <v>-29.88657424936666</v>
+        <v>-28.3697143315204</v>
       </c>
       <c r="F21">
-        <v>0.7064887312107038</v>
+        <v>1.888393401116205</v>
       </c>
       <c r="G21">
-        <v>-5.607711537597837</v>
+        <v>-4.187949937377025</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-13.74231305507533</v>
       </c>
       <c r="E22">
-        <v>-30.67158974707033</v>
+        <v>-29.54359442073672</v>
       </c>
       <c r="F22">
-        <v>0.7907999654676375</v>
+        <v>1.832293047129011</v>
       </c>
       <c r="G22">
-        <v>-6.210872247098084</v>
+        <v>-3.916064637739876</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-13.53961010932218</v>
       </c>
       <c r="E23">
-        <v>-30.56036816120494</v>
+        <v>-29.70307368986485</v>
       </c>
       <c r="F23">
-        <v>0.7282615400258861</v>
+        <v>2.526062344117236</v>
       </c>
       <c r="G23">
-        <v>-5.830903509292827</v>
+        <v>-3.873106885083626</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-13.33350421259369</v>
       </c>
       <c r="E24">
-        <v>-31.3017540760817</v>
+        <v>-31.63823328027364</v>
       </c>
       <c r="F24">
-        <v>1.076121176953094</v>
+        <v>2.934785447597735</v>
       </c>
       <c r="G24">
-        <v>-5.621489386925946</v>
+        <v>-3.348137685344947</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-13.12453052312097</v>
       </c>
       <c r="E25">
-        <v>-31.68120397013242</v>
+        <v>-30.48747784357748</v>
       </c>
       <c r="F25">
-        <v>1.412327341257718</v>
+        <v>2.590817480728879</v>
       </c>
       <c r="G25">
-        <v>-5.744883004890424</v>
+        <v>-2.784833974127276</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-12.9249559134853</v>
       </c>
       <c r="E26">
-        <v>-32.45669382276095</v>
+        <v>-31.6473649481101</v>
       </c>
       <c r="F26">
-        <v>1.353046056443774</v>
+        <v>2.835351538035293</v>
       </c>
       <c r="G26">
-        <v>-5.253992572268138</v>
+        <v>-3.374787766850757</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-12.73371462449664</v>
       </c>
       <c r="E27">
-        <v>-32.06352265246699</v>
+        <v>-31.53449273346892</v>
       </c>
       <c r="F27">
-        <v>1.541597387934192</v>
+        <v>2.632333598222385</v>
       </c>
       <c r="G27">
-        <v>-5.297212822649144</v>
+        <v>-3.722397097636771</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-12.55291721589646</v>
       </c>
       <c r="E28">
-        <v>-32.78465496734445</v>
+        <v>-31.46748716781443</v>
       </c>
       <c r="F28">
-        <v>1.395445213588664</v>
+        <v>2.936450466077362</v>
       </c>
       <c r="G28">
-        <v>-5.588450767043897</v>
+        <v>-2.948028809607818</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-12.3926572082482</v>
       </c>
       <c r="E29">
-        <v>-32.97897631548759</v>
+        <v>-32.05345585474794</v>
       </c>
       <c r="F29">
-        <v>1.333766633511018</v>
+        <v>3.031542073714328</v>
       </c>
       <c r="G29">
-        <v>-5.57076826406005</v>
+        <v>-3.042439397537721</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-12.24849506282761</v>
       </c>
       <c r="E30">
-        <v>-31.83834654667259</v>
+        <v>-31.65600754075374</v>
       </c>
       <c r="F30">
-        <v>1.226855879770908</v>
+        <v>3.018654333661574</v>
       </c>
       <c r="G30">
-        <v>-5.82166358938143</v>
+        <v>-4.532901478699888</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-12.11781824208464</v>
       </c>
       <c r="E31">
-        <v>-31.79887410298473</v>
+        <v>-32.04296790894617</v>
       </c>
       <c r="F31">
-        <v>1.246633979880149</v>
+        <v>2.688084381165597</v>
       </c>
       <c r="G31">
-        <v>-5.56597768058326</v>
+        <v>-4.141832368359029</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-12.00367951254304</v>
       </c>
       <c r="E32">
-        <v>-31.82635514750028</v>
+        <v>-31.54632790028797</v>
       </c>
       <c r="F32">
-        <v>1.230202484078218</v>
+        <v>2.611872923373237</v>
       </c>
       <c r="G32">
-        <v>-5.502978226641922</v>
+        <v>-4.694403203855757</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.89623568699663</v>
       </c>
       <c r="E33">
-        <v>-31.8562385474769</v>
+        <v>-32.21579259097491</v>
       </c>
       <c r="F33">
-        <v>1.321213553888994</v>
+        <v>2.473050143807679</v>
       </c>
       <c r="G33">
-        <v>-6.180704696080549</v>
+        <v>-3.663538545303452</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.78844159316894</v>
       </c>
       <c r="E34">
-        <v>-31.68479731425751</v>
+        <v>-30.18479690514179</v>
       </c>
       <c r="F34">
-        <v>1.27817986731356</v>
+        <v>3.03754939411943</v>
       </c>
       <c r="G34">
-        <v>-5.882001972638059</v>
+        <v>-3.742917857269538</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.67905307084365</v>
       </c>
       <c r="E35">
-        <v>-31.9178756071953</v>
+        <v>-31.81100135637727</v>
       </c>
       <c r="F35">
-        <v>1.21023882967075</v>
+        <v>2.362010806932016</v>
       </c>
       <c r="G35">
-        <v>-5.598809583507064</v>
+        <v>-3.527568005101622</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.55713805904244</v>
       </c>
       <c r="E36">
-        <v>-31.34114047876342</v>
+        <v>-30.98418804358281</v>
       </c>
       <c r="F36">
-        <v>1.421790610467299</v>
+        <v>2.702719976438259</v>
       </c>
       <c r="G36">
-        <v>-5.891855480981071</v>
+        <v>-3.541532884058619</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.41729381964657</v>
       </c>
       <c r="E37">
-        <v>-30.40485130683352</v>
+        <v>-28.50297826461812</v>
       </c>
       <c r="F37">
-        <v>1.188181062469005</v>
+        <v>2.582457596899827</v>
       </c>
       <c r="G37">
-        <v>-5.357574174456689</v>
+        <v>-3.010801859261555</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.26208396186698</v>
       </c>
       <c r="E38">
-        <v>-30.30516374426567</v>
+        <v>-28.58209523400613</v>
       </c>
       <c r="F38">
-        <v>1.389482625023313</v>
+        <v>2.259634536354831</v>
       </c>
       <c r="G38">
-        <v>-5.297248916086297</v>
+        <v>-3.843388861419736</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.08778687330904</v>
       </c>
       <c r="E39">
-        <v>-30.14127147721707</v>
+        <v>-29.85629007944037</v>
       </c>
       <c r="F39">
-        <v>1.084429702003173</v>
+        <v>2.480528644720153</v>
       </c>
       <c r="G39">
-        <v>-5.215474312381816</v>
+        <v>-3.951626517001138</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.89762001371104</v>
       </c>
       <c r="E40">
-        <v>-29.40325701123902</v>
+        <v>-28.95497884074572</v>
       </c>
       <c r="F40">
-        <v>1.210368054985587</v>
+        <v>1.944329738357644</v>
       </c>
       <c r="G40">
-        <v>-5.962139246784377</v>
+        <v>-3.25315944608526</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.70098410377079</v>
       </c>
       <c r="E41">
-        <v>-29.33986290360564</v>
+        <v>-27.83064025717331</v>
       </c>
       <c r="F41">
-        <v>1.265833879542236</v>
+        <v>2.201029199341572</v>
       </c>
       <c r="G41">
-        <v>-5.294361441113986</v>
+        <v>-4.106838140427552</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.50106765606059</v>
       </c>
       <c r="E42">
-        <v>-28.92942013344643</v>
+        <v>-26.62765113703568</v>
       </c>
       <c r="F42">
-        <v>1.167301233714041</v>
+        <v>2.159900757792576</v>
       </c>
       <c r="G42">
-        <v>-5.789025278529634</v>
+        <v>-3.880702912993741</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.30679107504863</v>
       </c>
       <c r="E43">
-        <v>-28.04356004806596</v>
+        <v>-26.90523753675786</v>
       </c>
       <c r="F43">
-        <v>1.129522709941966</v>
+        <v>2.446840599183103</v>
       </c>
       <c r="G43">
-        <v>-5.370059222490376</v>
+        <v>-3.543166932395222</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.12977171666223</v>
       </c>
       <c r="E44">
-        <v>-27.3713126101013</v>
+        <v>-27.07626894307955</v>
       </c>
       <c r="F44">
-        <v>1.282883337426656</v>
+        <v>2.504654016959286</v>
       </c>
       <c r="G44">
-        <v>-5.491260984453144</v>
+        <v>-2.688044500566776</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.973953934317629</v>
       </c>
       <c r="E45">
-        <v>-27.50245721736343</v>
+        <v>-26.43676690066436</v>
       </c>
       <c r="F45">
-        <v>1.259768573418938</v>
+        <v>2.134418519747658</v>
       </c>
       <c r="G45">
-        <v>-5.135455162211638</v>
+        <v>-3.143356647820002</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.845840400652332</v>
       </c>
       <c r="E46">
-        <v>-26.84438390304278</v>
+        <v>-24.5932523029858</v>
       </c>
       <c r="F46">
-        <v>1.0943800512456</v>
+        <v>2.137619331392075</v>
       </c>
       <c r="G46">
-        <v>-5.633977716181192</v>
+        <v>-3.642958723682614</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.751334076474928</v>
       </c>
       <c r="E47">
-        <v>-26.55420834557928</v>
+        <v>-25.81402474055155</v>
       </c>
       <c r="F47">
-        <v>1.168545441553046</v>
+        <v>2.216380504050252</v>
       </c>
       <c r="G47">
-        <v>-5.585021890514277</v>
+        <v>-2.511153846297111</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.689867916128847</v>
       </c>
       <c r="E48">
-        <v>-25.87910344051578</v>
+        <v>-25.05331809132106</v>
       </c>
       <c r="F48">
-        <v>1.154040728330026</v>
+        <v>1.925736203634407</v>
       </c>
       <c r="G48">
-        <v>-5.489777872308276</v>
+        <v>-2.820701006993566</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.661805873688138</v>
       </c>
       <c r="E49">
-        <v>-24.93761105195108</v>
+        <v>-24.87963752770488</v>
       </c>
       <c r="F49">
-        <v>0.9965250099528947</v>
+        <v>2.513981433914808</v>
       </c>
       <c r="G49">
-        <v>-5.25657489363542</v>
+        <v>-2.702314533128801</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.667808921291716</v>
       </c>
       <c r="E50">
-        <v>-24.75298516665836</v>
+        <v>-23.51299841387806</v>
       </c>
       <c r="F50">
-        <v>1.369237325698893</v>
+        <v>2.133623287040971</v>
       </c>
       <c r="G50">
-        <v>-5.231637609783641</v>
+        <v>-2.896680973424068</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.704084031456702</v>
       </c>
       <c r="E51">
-        <v>-24.59471500009028</v>
+        <v>-23.84379891166437</v>
       </c>
       <c r="F51">
-        <v>1.222243530072121</v>
+        <v>2.47987092100233</v>
       </c>
       <c r="G51">
-        <v>-5.916874795371838</v>
+        <v>-3.099778744289017</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.767641269557705</v>
       </c>
       <c r="E52">
-        <v>-23.35122773690205</v>
+        <v>-22.14608306313677</v>
       </c>
       <c r="F52">
-        <v>1.285476127397418</v>
+        <v>2.618060827872149</v>
       </c>
       <c r="G52">
-        <v>-5.165245372749836</v>
+        <v>-3.729973438217529</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.8576971001808</v>
       </c>
       <c r="E53">
-        <v>-23.08601312816883</v>
+        <v>-23.46669023867562</v>
       </c>
       <c r="F53">
-        <v>1.276099008397728</v>
+        <v>2.598153502448072</v>
       </c>
       <c r="G53">
-        <v>-5.792844620424827</v>
+        <v>-3.008416411187838</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.971985346735259</v>
       </c>
       <c r="E54">
-        <v>-22.91875846916954</v>
+        <v>-20.55647094612028</v>
       </c>
       <c r="F54">
-        <v>1.246340737819558</v>
+        <v>2.344953065373569</v>
       </c>
       <c r="G54">
-        <v>-6.136421329914284</v>
+        <v>-2.992909358097903</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.10806586722614</v>
       </c>
       <c r="E55">
-        <v>-22.86370128218428</v>
+        <v>-23.17853438061955</v>
       </c>
       <c r="F55">
-        <v>1.041919543626308</v>
+        <v>2.311874698244979</v>
       </c>
       <c r="G55">
-        <v>-6.219147487871004</v>
+        <v>-4.3560370742027</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.26479269904568</v>
       </c>
       <c r="E56">
-        <v>-22.29099423138222</v>
+        <v>-20.57226173498502</v>
       </c>
       <c r="F56">
-        <v>1.101172663948556</v>
+        <v>2.315481409916768</v>
       </c>
       <c r="G56">
-        <v>-6.28629768708504</v>
+        <v>-2.980854150088503</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.43990148798823</v>
       </c>
       <c r="E57">
-        <v>-22.11319728489307</v>
+        <v>-20.35907476412592</v>
       </c>
       <c r="F57">
-        <v>0.9563425639778963</v>
+        <v>2.198679949387232</v>
       </c>
       <c r="G57">
-        <v>-6.436712164591545</v>
+        <v>-3.941572854143</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.62896624636613</v>
       </c>
       <c r="E58">
-        <v>-21.00233091149348</v>
+        <v>-21.05623333760678</v>
       </c>
       <c r="F58">
-        <v>1.274813382188583</v>
+        <v>2.201711774081478</v>
       </c>
       <c r="G58">
-        <v>-6.358875026758398</v>
+        <v>-3.988323698921968</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.82866314678938</v>
       </c>
       <c r="E59">
-        <v>-21.02406305825629</v>
+        <v>-17.68564937743166</v>
       </c>
       <c r="F59">
-        <v>1.214178545038465</v>
+        <v>2.340292670365419</v>
       </c>
       <c r="G59">
-        <v>-6.686941401936358</v>
+        <v>-4.201521069746889</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.03561878690781</v>
       </c>
       <c r="E60">
-        <v>-20.57559016338066</v>
+        <v>-21.29656851014186</v>
       </c>
       <c r="F60">
-        <v>1.026152398481422</v>
+        <v>2.56436439608788</v>
       </c>
       <c r="G60">
-        <v>-7.273781315399927</v>
+        <v>-4.31360759821752</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.24179147906164</v>
       </c>
       <c r="E61">
-        <v>-20.15926490548549</v>
+        <v>-20.2670788146601</v>
       </c>
       <c r="F61">
-        <v>1.0981673470112</v>
+        <v>2.44189524578839</v>
       </c>
       <c r="G61">
-        <v>-7.006237071885923</v>
+        <v>-4.025946185322561</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.43998360921816</v>
       </c>
       <c r="E62">
-        <v>-19.57249241441561</v>
+        <v>-18.26418457428159</v>
       </c>
       <c r="F62">
-        <v>0.8036330332718075</v>
+        <v>2.146615401386478</v>
       </c>
       <c r="G62">
-        <v>-7.245776089390066</v>
+        <v>-3.92780484847957</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.62646077744853</v>
       </c>
       <c r="E63">
-        <v>-19.90196154084366</v>
+        <v>-18.97652712111016</v>
       </c>
       <c r="F63">
-        <v>0.9503319301031831</v>
+        <v>2.205172693090375</v>
       </c>
       <c r="G63">
-        <v>-7.240247231062402</v>
+        <v>-5.936043691722113</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.79134763982071</v>
       </c>
       <c r="E64">
-        <v>-18.79986682159693</v>
+        <v>-18.93477911923344</v>
       </c>
       <c r="F64">
-        <v>0.8772169096624876</v>
+        <v>2.068175635280587</v>
       </c>
       <c r="G64">
-        <v>-7.390372961071676</v>
+        <v>-5.735771052619846</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.92788396148099</v>
       </c>
       <c r="E65">
-        <v>-19.24048734254325</v>
+        <v>-17.34117741661619</v>
       </c>
       <c r="F65">
-        <v>0.7512884970889067</v>
+        <v>1.899952439854869</v>
       </c>
       <c r="G65">
-        <v>-7.725428338171255</v>
+        <v>-6.837867750006137</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-12.03538507016828</v>
       </c>
       <c r="E66">
-        <v>-19.13035485467671</v>
+        <v>-19.05121524291867</v>
       </c>
       <c r="F66">
-        <v>0.9430373267541307</v>
+        <v>1.701858315884201</v>
       </c>
       <c r="G66">
-        <v>-7.765557677843263</v>
+        <v>-5.50860224039481</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.10642717406847</v>
       </c>
       <c r="E67">
-        <v>-19.13543127403931</v>
+        <v>-19.10232812904324</v>
       </c>
       <c r="F67">
-        <v>0.8640823161236986</v>
+        <v>1.406906504973798</v>
       </c>
       <c r="G67">
-        <v>-8.068227398151121</v>
+        <v>-6.887660287170711</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.13760703661622</v>
       </c>
       <c r="E68">
-        <v>-18.40415970585868</v>
+        <v>-15.72117018206021</v>
       </c>
       <c r="F68">
-        <v>0.3448947627450804</v>
+        <v>1.707805993836301</v>
       </c>
       <c r="G68">
-        <v>-8.071059092356922</v>
+        <v>-5.489059284786757</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.13312621989088</v>
       </c>
       <c r="E69">
-        <v>-18.4304429689992</v>
+        <v>-18.14555666917666</v>
       </c>
       <c r="F69">
-        <v>0.0860274642680265</v>
+        <v>1.66959340554516</v>
       </c>
       <c r="G69">
-        <v>-8.444347263067151</v>
+        <v>-6.634494356530194</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.08909971569163</v>
       </c>
       <c r="E70">
-        <v>-17.63323229079288</v>
+        <v>-17.05977351330555</v>
       </c>
       <c r="F70">
-        <v>0.5754973370712124</v>
+        <v>0.9086882440296463</v>
       </c>
       <c r="G70">
-        <v>-8.024393559338501</v>
+        <v>-6.068260514459938</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.00590864663016</v>
       </c>
       <c r="E71">
-        <v>-18.36463518471973</v>
+        <v>-17.09913500938022</v>
       </c>
       <c r="F71">
-        <v>0.3129247512014363</v>
+        <v>1.296450338749706</v>
       </c>
       <c r="G71">
-        <v>-8.387221195717219</v>
+        <v>-5.591423553776754</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.89251526680746</v>
       </c>
       <c r="E72">
-        <v>-18.03642950253981</v>
+        <v>-16.06275297645879</v>
       </c>
       <c r="F72">
-        <v>0.2771177418480248</v>
+        <v>1.699641604714309</v>
       </c>
       <c r="G72">
-        <v>-8.128398439108219</v>
+        <v>-6.693047755258485</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.74916797399583</v>
       </c>
       <c r="E73">
-        <v>-18.21765450385277</v>
+        <v>-18.08194972326492</v>
       </c>
       <c r="F73">
-        <v>0.01858593216910475</v>
+        <v>1.147604313610274</v>
       </c>
       <c r="G73">
-        <v>-8.318863506969306</v>
+        <v>-6.289552658872009</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.57988446473372</v>
       </c>
       <c r="E74">
-        <v>-18.21695259038158</v>
+        <v>-16.90686505996255</v>
       </c>
       <c r="F74">
-        <v>0.1423001186750025</v>
+        <v>1.062421636845595</v>
       </c>
       <c r="G74">
-        <v>-7.749660159387753</v>
+        <v>-5.87756576108969</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.39676601230266</v>
       </c>
       <c r="E75">
-        <v>-18.90374548685888</v>
+        <v>-17.82146736986971</v>
       </c>
       <c r="F75">
-        <v>-0.1652122271640495</v>
+        <v>0.8133514396414512</v>
       </c>
       <c r="G75">
-        <v>-8.40204575472279</v>
+        <v>-6.107992826323255</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.20151510837501</v>
       </c>
       <c r="E76">
-        <v>-18.8703434625783</v>
+        <v>-17.36480699398822</v>
       </c>
       <c r="F76">
-        <v>-0.2726257999176586</v>
+        <v>0.3936872595047769</v>
       </c>
       <c r="G76">
-        <v>-7.270759310343678</v>
+        <v>-7.104450595603223</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.99847325095526</v>
       </c>
       <c r="E77">
-        <v>-18.75398432295122</v>
+        <v>-17.93749140242023</v>
       </c>
       <c r="F77">
-        <v>-0.1783103725371153</v>
+        <v>0.5422251319703675</v>
       </c>
       <c r="G77">
-        <v>-7.422463307923045</v>
+        <v>-5.715014045034798</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.79932866780266</v>
       </c>
       <c r="E78">
-        <v>-19.38315691615491</v>
+        <v>-17.94788425026784</v>
       </c>
       <c r="F78">
-        <v>-0.2900877847686722</v>
+        <v>0.2649896147036373</v>
       </c>
       <c r="G78">
-        <v>-7.90355601296883</v>
+        <v>-5.93854398255041</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.60447144689824</v>
       </c>
       <c r="E79">
-        <v>-19.07841325780873</v>
+        <v>-19.07934612345431</v>
       </c>
       <c r="F79">
-        <v>-0.1945016417922345</v>
+        <v>0.4128921293712806</v>
       </c>
       <c r="G79">
-        <v>-7.311512082111982</v>
+        <v>-6.412263782752122</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.4164708999481</v>
       </c>
       <c r="E80">
-        <v>-20.1026544519156</v>
+        <v>-20.65616982987315</v>
       </c>
       <c r="F80">
-        <v>-0.5150284678966696</v>
+        <v>0.2181992819565072</v>
       </c>
       <c r="G80">
-        <v>-6.989158313669014</v>
+        <v>-4.745600103847774</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.24390114994823</v>
       </c>
       <c r="E81">
-        <v>-20.6233746211096</v>
+        <v>-20.23807393864097</v>
       </c>
       <c r="F81">
-        <v>-0.5329800178827376</v>
+        <v>0.163642176440729</v>
       </c>
       <c r="G81">
-        <v>-7.15534562321177</v>
+        <v>-4.817258701484486</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.08414440088614</v>
       </c>
       <c r="E82">
-        <v>-21.24464502716991</v>
+        <v>-20.63625812966142</v>
       </c>
       <c r="F82">
-        <v>-0.4576234352500667</v>
+        <v>-0.398357889416776</v>
       </c>
       <c r="G82">
-        <v>-6.447313791450111</v>
+        <v>-4.723793105363704</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.936400682775918</v>
       </c>
       <c r="E83">
-        <v>-22.18880468692513</v>
+        <v>-21.60085932108727</v>
       </c>
       <c r="F83">
-        <v>-0.5497188379911073</v>
+        <v>0.2097847258788698</v>
       </c>
       <c r="G83">
-        <v>-6.505755628645381</v>
+        <v>-5.53814635931605</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.80528984375462</v>
       </c>
       <c r="E84">
-        <v>-22.82075776316954</v>
+        <v>-22.37816735602988</v>
       </c>
       <c r="F84">
-        <v>-0.6169342257890648</v>
+        <v>0.474633665371539</v>
       </c>
       <c r="G84">
-        <v>-6.509798093606617</v>
+        <v>-5.320558714044592</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.685294244570056</v>
       </c>
       <c r="E85">
-        <v>-23.95149055204078</v>
+        <v>-23.16325983779167</v>
       </c>
       <c r="F85">
-        <v>-0.6289795161931724</v>
+        <v>-0.03038052174517962</v>
       </c>
       <c r="G85">
-        <v>-6.190850233142353</v>
+        <v>-5.41730881294638</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.574018058993646</v>
       </c>
       <c r="E86">
-        <v>-24.52575086942747</v>
+        <v>-24.57024312655283</v>
       </c>
       <c r="F86">
-        <v>-0.6478720915488206</v>
+        <v>0.1898020190211374</v>
       </c>
       <c r="G86">
-        <v>-5.72026071830835</v>
+        <v>-4.27183108532267</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.474107107816918</v>
       </c>
       <c r="E87">
-        <v>-25.92829625366111</v>
+        <v>-25.71411301852032</v>
       </c>
       <c r="F87">
-        <v>-0.5160995469484894</v>
+        <v>-0.09540322102792681</v>
       </c>
       <c r="G87">
-        <v>-5.660644203794799</v>
+        <v>-3.68996550374322</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.379796266092763</v>
       </c>
       <c r="E88">
-        <v>-26.96104645042839</v>
+        <v>-25.65568211839935</v>
       </c>
       <c r="F88">
-        <v>-1.085849818226587</v>
+        <v>-0.2550958889396155</v>
       </c>
       <c r="G88">
-        <v>-5.353620302477558</v>
+        <v>-4.137898183709256</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.289251803808519</v>
       </c>
       <c r="E89">
-        <v>-28.98651513373514</v>
+        <v>-28.66241224900617</v>
       </c>
       <c r="F89">
-        <v>-0.7135574847538075</v>
+        <v>-0.3926860578098078</v>
       </c>
       <c r="G89">
-        <v>-5.914479503633443</v>
+        <v>-3.875485770714224</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.204793725714772</v>
       </c>
       <c r="E90">
-        <v>-30.08443912842081</v>
+        <v>-30.06767698188142</v>
       </c>
       <c r="F90">
-        <v>-0.89900326685113</v>
+        <v>-0.1104720524522526</v>
       </c>
       <c r="G90">
-        <v>-5.221104888577823</v>
+        <v>-3.951327925839229</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.121800067262496</v>
       </c>
       <c r="E91">
-        <v>-31.61245720622198</v>
+        <v>-31.86593853880132</v>
       </c>
       <c r="F91">
-        <v>-1.141560839534465</v>
+        <v>-0.280333758600708</v>
       </c>
       <c r="G91">
-        <v>-5.556855884648003</v>
+        <v>-3.518682457118646</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.0403174621208</v>
       </c>
       <c r="E92">
-        <v>-33.02443313757659</v>
+        <v>-35.21736705392399</v>
       </c>
       <c r="F92">
-        <v>-1.321537740038505</v>
+        <v>-0.9032163434617683</v>
       </c>
       <c r="G92">
-        <v>-5.212140591277421</v>
+        <v>-3.804240606994</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.963508042259575</v>
       </c>
       <c r="E93">
-        <v>-34.57782425524273</v>
+        <v>-33.57925498028535</v>
       </c>
       <c r="F93">
-        <v>-1.139940552894589</v>
+        <v>-0.6357224268519603</v>
       </c>
       <c r="G93">
-        <v>-5.022180831536487</v>
+        <v>-3.710847197747526</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.888083456927182</v>
       </c>
       <c r="E94">
-        <v>-36.40896706193233</v>
+        <v>-36.22759488521412</v>
       </c>
       <c r="F94">
-        <v>-1.251352655101511</v>
+        <v>-1.135290926662675</v>
       </c>
       <c r="G94">
-        <v>-5.83454566522381</v>
+        <v>-3.681001206442816</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.815166399496716</v>
       </c>
       <c r="E95">
-        <v>-37.86896519590129</v>
+        <v>-37.49042326088911</v>
       </c>
       <c r="F95">
-        <v>-1.237793109085086</v>
+        <v>-0.6960963282701967</v>
       </c>
       <c r="G95">
-        <v>-5.831960062634968</v>
+        <v>-4.383290900475448</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.747237074738957</v>
       </c>
       <c r="E96">
-        <v>-40.67485976850493</v>
+        <v>-39.63000043224114</v>
       </c>
       <c r="F96">
-        <v>-1.457632705746644</v>
+        <v>-1.538497931607931</v>
       </c>
       <c r="G96">
-        <v>-5.980763460355785</v>
+        <v>-4.888366053899213</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.682032344430974</v>
       </c>
       <c r="E97">
-        <v>-42.37997514356106</v>
+        <v>-43.59376240996998</v>
       </c>
       <c r="F97">
-        <v>-1.667117709873208</v>
+        <v>-1.494561324563446</v>
       </c>
       <c r="G97">
-        <v>-6.095235436900134</v>
+        <v>-3.621817813175112</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.619551814904799</v>
       </c>
       <c r="E98">
-        <v>-44.20426410484006</v>
+        <v>-43.21957233847918</v>
       </c>
       <c r="F98">
-        <v>-1.801128503195904</v>
+        <v>-1.173366834332354</v>
       </c>
       <c r="G98">
-        <v>-6.58942677841122</v>
+        <v>-4.578900923741744</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.559454140013722</v>
       </c>
       <c r="E99">
-        <v>-46.14455445629953</v>
+        <v>-45.98728055401314</v>
       </c>
       <c r="F99">
-        <v>-1.88269452787996</v>
+        <v>-1.289245493575172</v>
       </c>
       <c r="G99">
-        <v>-6.810049553625165</v>
+        <v>-5.002093193149567</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.499196779769456</v>
       </c>
       <c r="E100">
-        <v>-48.88763343382428</v>
+        <v>-46.12010748936913</v>
       </c>
       <c r="F100">
-        <v>-1.99130674826542</v>
+        <v>-2.245587376433173</v>
       </c>
       <c r="G100">
-        <v>-7.043213157639306</v>
+        <v>-6.211958331434261</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.433300082381733</v>
       </c>
       <c r="E101">
-        <v>-49.72715024832875</v>
+        <v>-50.27229247784612</v>
       </c>
       <c r="F101">
-        <v>-2.257717988679769</v>
+        <v>-2.041384871234261</v>
       </c>
       <c r="G101">
-        <v>-7.615697726780304</v>
+        <v>-5.550464065050205</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.359288504457153</v>
       </c>
       <c r="E102">
-        <v>-52.56170666504544</v>
+        <v>-51.79844256011912</v>
       </c>
       <c r="F102">
-        <v>-2.409250409306479</v>
+        <v>-2.247167073070311</v>
       </c>
       <c r="G102">
-        <v>-7.58399128285139</v>
+        <v>-6.088745180655551</v>
       </c>
     </row>
   </sheetData>
